--- a/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 7,23</t>
+          <t>-9,93; 8,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 11,02</t>
+          <t>-8,87; 9,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 19,31</t>
+          <t>1,79; 19,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,93</t>
+          <t>-7,68; 0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,97; 168,77</t>
+          <t>-69,95; 176,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 180,38</t>
+          <t>-61,7; 185,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1117,98</t>
+          <t>-4,13; 1077,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 9,24</t>
+          <t>-3,51; 9,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 6,59</t>
+          <t>-5,53; 5,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 6,57</t>
+          <t>-8,23; 6,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 4,36</t>
+          <t>-5,64; 4,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 187,33</t>
+          <t>-38,78; 200,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 200,63</t>
+          <t>-66,18; 168,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 77,53</t>
+          <t>-50,26; 72,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,47; 386,38</t>
+          <t>-86,02; 319,35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 8,27</t>
+          <t>-9,48; 9,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 7,48</t>
+          <t>-13,34; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 5,61</t>
+          <t>-9,2; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 12,03</t>
+          <t>-6,18; 10,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 96,48</t>
+          <t>-55,58; 102,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 59,18</t>
+          <t>-61,48; 47,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 138,12</t>
+          <t>-75,57; 150,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,81; 340,8</t>
+          <t>-61,07; 295,06</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 19,11</t>
+          <t>-1,4; 18,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,14</t>
+          <t>-3,72; 5,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 4,1</t>
+          <t>-12,28; 3,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 10,0</t>
+          <t>-7,72; 9,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 217,12</t>
+          <t>-7,7; 225,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,85; 693,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 51,96</t>
+          <t>-71,56; 52,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 418,89</t>
+          <t>-66,63; 556,95</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,67</t>
+          <t>-1,53; 10,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 9,28</t>
+          <t>-7,53; 10,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 0,0</t>
+          <t>-6,38; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 0,44</t>
+          <t>-16,14; 0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 579,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,7</t>
+          <t>-100,0; 69,02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 10,54</t>
+          <t>-10,83; 11,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 11,29</t>
+          <t>-14,12; 10,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,31</t>
+          <t>-2,58; 6,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 18,08</t>
+          <t>-12,31; 17,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 82,37</t>
+          <t>-47,79; 87,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 66,36</t>
+          <t>-51,23; 57,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 71,18</t>
+          <t>-30,98; 70,63</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 8,78</t>
+          <t>-3,78; 8,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 9,18</t>
+          <t>-5,27; 9,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,94</t>
+          <t>-7,87; 4,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 3,25</t>
+          <t>-8,31; 3,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 134,22</t>
+          <t>-33,63; 131,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 80,61</t>
+          <t>-28,39; 81,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 52,57</t>
+          <t>-55,84; 64,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 55,33</t>
+          <t>-66,57; 65,15</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,59</t>
+          <t>-3,67; 5,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 2,79</t>
+          <t>-6,22; 3,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,38</t>
+          <t>-3,63; 7,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 1,33</t>
+          <t>-12,42; 1,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 130,61</t>
+          <t>-44,64; 153,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 45,67</t>
+          <t>-55,2; 59,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 92,88</t>
+          <t>-27,93; 102,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 10,65</t>
+          <t>-58,64; 13,12</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,05</t>
+          <t>-0,54; 4,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,11</t>
+          <t>-3,31; 2,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,38</t>
+          <t>-2,4; 2,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,84</t>
+          <t>-4,7; 0,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 59,8</t>
+          <t>-4,87; 56,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 22,23</t>
+          <t>-27,02; 22,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 29,0</t>
+          <t>-23,71; 31,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 8,52</t>
+          <t>-38,63; 8,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 8,32</t>
+          <t>-10,35; 6,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 9,97</t>
+          <t>-10,09; 9,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 19,13</t>
+          <t>2,37; 19,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,93</t>
+          <t>-7,68; 0,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,95; 176,33</t>
+          <t>-71,2; 134,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 185,14</t>
+          <t>-64,65; 139,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1077,99</t>
+          <t>1,17; 1158,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 9,02</t>
+          <t>-2,85; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,49</t>
+          <t>-4,81; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 6,52</t>
+          <t>-8,93; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,14</t>
+          <t>-5,6; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 200,54</t>
+          <t>-32,95; 200,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 168,96</t>
+          <t>-66,04; 174,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 72,72</t>
+          <t>-52,89; 66,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,02; 319,35</t>
+          <t>-82,23; 445,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 9,2</t>
+          <t>-9,61; 9,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 6,26</t>
+          <t>-14,13; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 6,27</t>
+          <t>-9,34; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 10,82</t>
+          <t>-6,61; 10,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 102,41</t>
+          <t>-58,43; 114,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 47,06</t>
+          <t>-60,67; 49,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 150,86</t>
+          <t>-79,25; 147,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 295,06</t>
+          <t>-53,74; 246,11</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 18,07</t>
+          <t>-0,32; 18,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,87</t>
+          <t>-3,29; 5,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 3,69</t>
+          <t>-13,0; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 9,75</t>
+          <t>-7,7; 9,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 225,95</t>
+          <t>-6,07; 211,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 52,65</t>
+          <t>-71,29; 43,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,63; 556,95</t>
+          <t>-66,5; 632,21</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,51</t>
+          <t>-1,53; 11,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 10,03</t>
+          <t>-7,89; 9,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,0</t>
+          <t>-7,68; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 0,43</t>
+          <t>-15,95; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,02</t>
+          <t>-100,0; 74,87</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 11,17</t>
+          <t>-10,79; 12,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 10,25</t>
+          <t>-15,99; 9,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,03</t>
+          <t>-2,56; 6,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 17,64</t>
+          <t>-11,59; 16,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 87,16</t>
+          <t>-47,61; 90,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 57,73</t>
+          <t>-54,93; 59,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 70,63</t>
+          <t>-28,62; 69,01</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 8,78</t>
+          <t>-3,32; 8,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 9,09</t>
+          <t>-5,22; 9,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 4,66</t>
+          <t>-8,29; 3,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 3,76</t>
+          <t>-7,95; 4,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 131,72</t>
+          <t>-30,3; 130,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 81,29</t>
+          <t>-29,18; 76,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 64,57</t>
+          <t>-57,7; 49,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 65,15</t>
+          <t>-62,91; 69,52</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,96</t>
+          <t>-3,11; 5,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,12</t>
+          <t>-6,06; 3,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 7,91</t>
+          <t>-3,62; 7,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 1,95</t>
+          <t>-13,31; 1,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 153,7</t>
+          <t>-39,73; 116,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 59,87</t>
+          <t>-58,48; 63,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 102,61</t>
+          <t>-28,99; 85,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 13,12</t>
+          <t>-58,48; 14,4</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,62</t>
+          <t>-0,57; 4,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,04</t>
+          <t>-3,2; 2,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,56</t>
+          <t>-2,4; 2,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,82</t>
+          <t>-4,9; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 56,73</t>
+          <t>-5,53; 56,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 22,26</t>
+          <t>-26,11; 21,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 31,76</t>
+          <t>-23,06; 35,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 8,11</t>
+          <t>-39,27; 9,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-70,43%</t>
+          <t>-67,56%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 6,81</t>
+          <t>-10,07; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 9,17</t>
+          <t>-8,43; 11,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 19,16</t>
+          <t>1,84; 19,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,9</t>
+          <t>-7,88; 1,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 134,51</t>
+          <t>-73,97; 168,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 139,34</t>
+          <t>-58,17; 180,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1158,62</t>
+          <t>0,81; 1117,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,68%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 8,91</t>
+          <t>-3,42; 9,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,84</t>
+          <t>-4,71; 6,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 5,94</t>
+          <t>-8,27; 6,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,57</t>
+          <t>-4,79; 5,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 200,82</t>
+          <t>-34,27; 187,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 174,29</t>
+          <t>-62,12; 200,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 66,69</t>
+          <t>-51,41; 77,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,23; 445,74</t>
+          <t>-77,15; 495,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 9,42</t>
+          <t>-10,4; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 6,07</t>
+          <t>-13,13; 7,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 6,26</t>
+          <t>-8,99; 5,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 10,21</t>
+          <t>-4,29; 13,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 114,25</t>
+          <t>-58,29; 96,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 49,83</t>
+          <t>-59,4; 59,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 147,97</t>
+          <t>-76,78; 138,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 246,11</t>
+          <t>-45,89; 395,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 18,72</t>
+          <t>-0,52; 19,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,69</t>
+          <t>-3,63; 5,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 4,17</t>
+          <t>-12,67; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 9,94</t>
+          <t>-8,98; 9,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 211,8</t>
+          <t>-7,34; 217,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,85; 693,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 43,82</t>
+          <t>-69,91; 51,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 632,21</t>
+          <t>-68,67; 425,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,78</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-69,39%</t>
+          <t>-71,27%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 11,31</t>
+          <t>-1,52; 11,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 9,39</t>
+          <t>-7,56; 9,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,0</t>
+          <t>-6,24; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 0,51</t>
+          <t>-15,54; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 579,14</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,87</t>
+          <t>-100,0; 120,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 12,44</t>
+          <t>-11,74; 10,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 9,99</t>
+          <t>-15,51; 11,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,28</t>
+          <t>-2,58; 6,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 16,84</t>
+          <t>-11,9; 17,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 90,02</t>
+          <t>-49,88; 82,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 59,21</t>
+          <t>-52,85; 66,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 69,01</t>
+          <t>-31,67; 73,35</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-22,6%</t>
+          <t>-28,75%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 8,75</t>
+          <t>-3,44; 8,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 9,24</t>
+          <t>-5,37; 9,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,98</t>
+          <t>-7,88; 3,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 4,28</t>
+          <t>-8,9; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 130,74</t>
+          <t>-28,44; 134,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 76,27</t>
+          <t>-29,38; 80,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 49,95</t>
+          <t>-56,62; 52,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 69,52</t>
+          <t>-64,36; 43,94</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-5,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-32,48%</t>
+          <t>-31,89%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,58</t>
+          <t>-3,23; 5,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,32</t>
+          <t>-6,78; 2,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,33</t>
+          <t>-3,54; 7,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 1,53</t>
+          <t>-13,26; 1,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 116,06</t>
+          <t>-40,48; 130,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 63,27</t>
+          <t>-60,43; 45,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 85,12</t>
+          <t>-28,26; 92,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 14,4</t>
+          <t>-58,53; 12,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-14,26%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,71</t>
+          <t>-0,24; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,0</t>
+          <t>-2,94; 2,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,81</t>
+          <t>-2,42; 2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,88</t>
+          <t>-4,57; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 56,3</t>
+          <t>-2,57; 59,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 21,34</t>
+          <t>-24,57; 22,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 35,39</t>
+          <t>-23,05; 29,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 9,51</t>
+          <t>-34,55; 11,25</t>
         </is>
       </c>
     </row>
